--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="263">
   <si>
     <t>ID</t>
   </si>
@@ -777,6 +777,18 @@
   </si>
   <si>
     <t>Ricevuta del pagamento</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Verbale di giuramento pervenuto da consolato</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Copia integrale dell'atto di nascita del genitore oppure Certificato di cittadinanza per nascita del genitore</t>
   </si>
   <si>
     <t>998</t>
@@ -847,11 +859,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="94.6640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="94.703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.55859375" customWidth="true" bestFit="true"/>
@@ -2956,7 +2968,7 @@
         <v>256</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>8</v>
@@ -2973,13 +2985,47 @@
         <v>258</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>257</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="266">
   <si>
     <t>ID</t>
   </si>
@@ -789,6 +789,15 @@
   </si>
   <si>
     <t>Copia integrale dell'atto di nascita del genitore oppure Certificato di cittadinanza per nascita del genitore</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Nota di trasmissione da parte di altro comune</t>
+  </si>
+  <si>
+    <t>2026-01-01 00:00:00.0</t>
   </si>
   <si>
     <t>998</t>
@@ -859,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -3002,7 +3011,7 @@
         <v>260</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>7</v>
+        <v>261</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -3013,19 +3022,36 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>261</v>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="264">
   <si>
     <t>ID</t>
   </si>
@@ -116,7 +116,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Copia dell'atto di dichiarazione/assenso del figlio</t>
+    <t>Copia dell'atto di assenso del figlio</t>
   </si>
   <si>
     <t>15</t>
@@ -362,13 +362,13 @@
     <t>56</t>
   </si>
   <si>
-    <t>Verbale di richiesta dell'unione civile 1</t>
+    <t>Certificato della richiesta di costituzione 1</t>
   </si>
   <si>
     <t>57</t>
   </si>
   <si>
-    <t>Verbale di richiesta dell'unione civile 2</t>
+    <t>Certificato della richiesta di costituzione 2</t>
   </si>
   <si>
     <t>58</t>
@@ -647,7 +647,7 @@
     <t>Provvedimento di rifiuto</t>
   </si>
   <si>
-    <t>2024-05-29 00:00:00.0</t>
+    <t>2024-05-30 00:00:00.0</t>
   </si>
   <si>
     <t>103</t>
@@ -665,7 +665,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>Processo Verbale (Redatto in luogo particolare da autorità incaricata)</t>
+    <t>Processo Verbale (Redatto in luogo particolare da autorit� incaricata)</t>
   </si>
   <si>
     <t>106</t>
@@ -678,12 +678,6 @@
   </si>
   <si>
     <t>Certificato medico</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Negoziazione assistita e nulla osta o autorizzazione</t>
   </si>
   <si>
     <t>109</t>
@@ -868,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -2722,7 +2716,7 @@
         <v>225</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
@@ -2733,19 +2727,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="D110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="111">
@@ -2756,7 +2750,7 @@
         <v>230</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>8</v>
@@ -2773,7 +2767,7 @@
         <v>232</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>8</v>
@@ -2994,7 +2988,7 @@
         <v>258</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>8</v>
@@ -3005,19 +2999,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="127">
@@ -3035,23 +3029,6 @@
       </c>
       <c r="E127" s="2" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="269">
   <si>
     <t>ID</t>
   </si>
@@ -792,6 +792,21 @@
   </si>
   <si>
     <t>2026-01-01 00:00:00.0</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Documento autorizzativo</t>
+  </si>
+  <si>
+    <t>2026-06-04 09:35:50.0</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Sentenza rettifica sesso</t>
   </si>
   <si>
     <t>998</t>
@@ -862,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -3005,7 +3020,7 @@
         <v>261</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -3016,19 +3031,53 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>262</v>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
